--- a/docs/spec.xlsx
+++ b/docs/spec.xlsx
@@ -34,7 +34,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="1025">
   <si>
-    <t xml:space="preserve">기능 명세 · API 명세 (새 탭 북마크 도구)</t>
+    <t xml:space="preserve">기능 명세 · API 명세 (바로링크 BaroLink · 새 탭 북마크 도구)</t>
   </si>
   <si>
     <t xml:space="preserve">기준 문서</t>
@@ -53,7 +53,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026-10-07 · v13 (v2: </t>
+      <t xml:space="preserve">2026-10-07 · v14 (v2: </t>
     </r>
     <r>
       <rPr>
@@ -1064,16 +1064,84 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">번</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">번 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ v14: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서비스 이름을 바로링크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(BaroLink)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 확정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가져오기 폴더는 한국어 크롬의 파일 가져오기만 다룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(F05-04, N19). suggestForNew</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 출력을 북마크별 추천 폴더 하나로 정리하고 추천 방법을 적음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(N24, F10-07))</t>
     </r>
   </si>
   <si>
@@ -5870,7 +5938,7 @@
   </si>
   <si>
     <t xml:space="preserve">수정(v9): 북마크바를 기본 정리 대상에 포함(크롬 별 버튼의 기본 저장 위치가 북마크바). 요즘 쓰는 북마크는 폴더에 넣지 않고 카테고리 개수에도 세지 않음 / 확정(v5): 기타 북마크가 계정용·이 PC 전용 두 개면 한쪽(동기화되는 쪽)만 정리 대상으로 삼음. 이 PC 전용 북마크를 계정 쪽으로 옮기면 사용자 모르게 계정에 올라가기 때문
-확정(v12, 10월 7일): 크롬 가져오기 폴더는 사용자 폴더로 보지 않는다. 실행 확인: 북마크가 없는 새 프로필에 HTML을 가져오면 북마크바 항목은 북마크바에 그대로, 나머지는 기타 북마크가 아니라 북마크바 맨 끝의 "가져온 북마크" 폴더에 들어감. 다른 브라우저에서 옮겨 온 사용자도 같은 폴더를 가짐. 크롬이 가져오기 폴더에 따로 표시를 남기지 않아 폴더 이름으로 판단함. 이름 목록: "가져온 북마크"(한국어 크롬에서 HTML 가져오기로 확인, 10월 7일). 확인 필요: 영어 크롬의 "Imported", 다른 브라우저에서 가져온 경우의 "Imported From …"·"…에서 가져옴", 같은 이름이 이미 있을 때 뒤에 붙는 " (1)" 같은 번호. 가져오기 폴더 안의 폴더는 사용자 폴더로 봄. 사용자가 같은 이름의 폴더를 직접 만들었으면 그 폴더도 대상이 되는 한계가 있음(첫 정리 카드에서 미리 보여 주고 되돌릴 수 있음). 화면에서는 가져오기 폴더도 보통 앱 폴더로 표시(F03-01)</t>
+확정(v12, 10월 7일): 크롬 가져오기 폴더는 사용자 폴더로 보지 않는다. 실행 확인: 북마크가 없는 새 프로필에 HTML을 가져오면 북마크바 항목은 북마크바에 그대로, 나머지는 기타 북마크가 아니라 북마크바 맨 끝의 "가져온 북마크" 폴더에 들어감. 다른 브라우저에서 옮겨 온 사용자도 같은 폴더를 가짐. 크롬이 가져오기 폴더에 따로 표시를 남기지 않아 폴더 이름으로 판단함. 이름 목록: "가져온 북마크"(한국어 크롬에서 HTML 가져오기로 확인, 10월 7일). 범위(v14): 한국어 크롬의 파일 가져오기("가져온 북마크")만 다룬다. 영어 크롬의 "Imported", 다른 브라우저의 북마크를 크롬으로 가져왔을 때의 "Imported From Firefox" 같은 이름, 이름 뒤에 붙는 번호는 팀이 확인할 수 없어 다루지 않는다. 그런 폴더는 사용자 폴더로 취급되어 정리 대상에서 빠진다. 가져오기 폴더 안의 폴더는 사용자 폴더로 봄. 사용자가 같은 이름의 폴더를 직접 만들었으면 그 폴더도 대상이 되는 한계가 있음(첫 정리 카드에서 미리 보여 주고 되돌릴 수 있음). 화면에서는 가져오기 폴더도 보통 앱 폴더로 표시(F03-01)</t>
   </si>
   <si>
     <t xml:space="preserve">F05-05</t>
@@ -10985,7 +11053,8 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">제안: 추천 폴더가 없을 때의 기본값</t>
+    <t xml:space="preserve">제안: 추천 폴더가 없을 때의 기본값
+확정(v14): 추천 폴더는 분류된 카테고리와 이름이 같은 폴더다(classify.js의 suggestForNew, N24). 없으면 그대로 두기</t>
   </si>
   <si>
     <t xml:space="preserve">F10-08</t>
@@ -17623,16 +17692,67 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확인 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
+      <t xml:space="preserve">범위</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(v14): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한국어 크롬의 파일 가져오기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가져온 북마크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 다룬다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -17657,58 +17777,58 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">다른 브라우저에서 가져온 경우의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"Imported From …"·"…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에서 가져옴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">", </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 이름이 이미 있을 때 뒤에 붙는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">" (1)" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 번호</t>
+      <t xml:space="preserve">다른 브라우저의 북마크를 크롬으로 가져왔을 때의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Imported From Firefox" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 이름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이름 뒤에 붙는 번호는 팀이 확인할 수 없어 다루지 않는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그런 폴더는 사용자 폴더로 취급되어 정리 대상에서 빠진다</t>
     </r>
   </si>
   <si>
@@ -17967,39 +18087,49 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">[{ bookmarkId, folderId </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">또는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">null }], </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">새 폴더 제안</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">새 북마크마다 추천 폴더를 정함</t>
-  </si>
-  <si>
-    <t xml:space="preserve">추천할 폴더가 없으면 folderId: null (그대로 두기)</t>
+      <t xml:space="preserve">[{ bookmarkId, folderId }] (folderId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이면 그대로 두기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">새 북마크마다 분류해, 분류된 카테고리와 이름이 같은 폴더를 추천 폴더로 정함</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추천할 폴더가 없으면 folderId: null (그대로 두기). 분류되지 않았거나 같은 이름의 폴더가 없으면 null
+v14: 출력은 북마크별 추천 폴더 하나뿐. 새 폴더를 만들자는 제안은 plan.js의 suggestNewFolders(N37)가 맡음. 폴더를 이름으로 찾으므로, 사용자가 폴더 이름을 바꿨으면 추천이 null(그대로 두기)이 되는 한계가 있음</t>
   </si>
   <si>
     <t xml:space="preserve">N25</t>

--- a/docs/spec.xlsx
+++ b/docs/spec.xlsx
@@ -53,7 +53,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026-10-07 · v14 (v2: </t>
+      <t xml:space="preserve">2026-10-25 · v15 (v2: </t>
     </r>
     <r>
       <rPr>
@@ -1141,7 +1141,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(N24, F10-07))</t>
+      <t xml:space="preserve">(N24, F10-07) / v15: hasFavicon의 출력을 true·false에서 쓸 파비콘 주소 또는 null로 바꿈. 첫 페이지 주소에서 찾았을 때 appIcon이 그 주소로 그리게 함(N07, N44))</t>
     </r>
   </si>
   <si>
@@ -16582,7 +16582,7 @@
     <t xml:space="preserve">주소, 크기 / 주소</t>
   </si>
   <si>
-    <t xml:space="preserve">이미지 주소 / true·false</t>
+    <t xml:space="preserve">이미지 주소 / 쓸 파비콘 주소 또는 null</t>
   </si>
   <si>
     <r>

--- a/docs/spec.xlsx
+++ b/docs/spec.xlsx
@@ -53,7 +53,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026-10-25 · v15 (v2: </t>
+      <t xml:space="preserve">2026-10-29 · v16 (v2: </t>
     </r>
     <r>
       <rPr>
@@ -1141,7 +1141,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(N24, F10-07) / v15: hasFavicon의 출력을 true·false에서 쓸 파비콘 주소 또는 null로 바꿈. 첫 페이지 주소에서 찾았을 때 appIcon이 그 주소로 그리게 함(N07, N44))</t>
+      <t xml:space="preserve">(N24, F10-07) / v15: hasFavicon의 출력을 true·false에서 쓸 파비콘 주소 또는 null로 바꿈. 첫 페이지 주소에서 찾았을 때 appIcon이 그 주소로 그리게 함(N07, N44) / v16: N14 setPending 입력 필드 이름을 { id, toParentId }로 확정)</t>
     </r>
   </si>
   <si>
@@ -16808,7 +16808,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">[{</t>
+      <t xml:space="preserve">[{ id: </t>
     </r>
     <r>
       <rPr>
@@ -16825,6 +16825,40 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">ID, toParentId: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목적지 폴더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ID }] / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">북마크 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">ID, </t>
     </r>
     <r>
@@ -16833,40 +16867,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">목적지 폴더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">}] / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">북마크 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ID, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">옮겨진 폴더</t>
     </r>
   </si>
@@ -17022,7 +17022,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">옮기기 시작</t>
+      <t xml:space="preserve">옮기기 시작. ID는 문자열로 맞춤. 항목에 id나 toParentId가 없으면 오류.</t>
     </r>
   </si>
   <si>
